--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484624_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484624_PROCESSED_CHRONO.xlsx
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3035</v>
+        <v>0.7695</v>
       </c>
       <c r="E3" t="n">
-        <v>1.855</v>
+        <v>1.9651</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5515</v>
+        <v>-1.1956</v>
       </c>
       <c r="G3" t="n">
         <v>-1.6065</v>
@@ -688,13 +688,13 @@
         <v>1.6493</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9099</v>
+        <v>0.3759</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6207</v>
+        <v>0.7308</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2893</v>
+        <v>-0.3549</v>
       </c>
       <c r="V3" t="n">
         <v>1.267</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3368</v>
+        <v>0.3919</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0907</v>
+        <v>2.1458</v>
       </c>
       <c r="F4" t="n">
         <v>-1.7539</v>
@@ -766,10 +766,10 @@
         <v>1.4661</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6418</v>
+        <v>-0.5867</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1666</v>
+        <v>-0.1116</v>
       </c>
       <c r="U4" t="n">
         <v>-0.4751</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0388</v>
+        <v>0.2643</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1276</v>
+        <v>0.0236</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1664</v>
+        <v>0.2407</v>
       </c>
       <c r="G5" t="n">
         <v>0.8609</v>
@@ -844,13 +844,13 @@
         <v>0.5498</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1337</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.07389999999999999</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0598</v>
+        <v>0.0145</v>
       </c>
       <c r="V5" t="n">
         <v>-0.3219</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. MONDRAGON VIDAL</t>
+          <t>A. MARTIN MARGARIT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3</v>
+        <v>-0.3119</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7954</v>
+        <v>1.2441</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.0954</v>
+        <v>-1.5559</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8686</v>
+        <v>-0.3611</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7277</v>
+        <v>0.5815</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.5964</v>
+        <v>-0.9426</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3664</v>
+        <v>1.4922</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2633</v>
+        <v>1.4088</v>
       </c>
       <c r="L6" t="n">
-        <v>0.103</v>
+        <v>0.0833</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.235</v>
+        <v>-1.8532</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5356</v>
+        <v>-0.8273</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.6994</v>
+        <v>-1.0259</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9163</v>
+        <v>1.0995</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8326</v>
+        <v>1.0995</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0361</v>
+        <v>-0.4169</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0234</v>
+        <v>-0.2481</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0595</v>
+        <v>-0.1687</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3115</v>
+        <v>-0.6335</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>-0.6335</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. MARTIN MARGARIT</t>
+          <t>B. MONDRAGON VIDAL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4354</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9967</v>
+        <v>2.3286</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4321</v>
+        <v>-2.8725</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3611</v>
+        <v>-0.8686</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5815</v>
+        <v>0.7277</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9426</v>
+        <v>-1.5964</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4922</v>
+        <v>2.3664</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4088</v>
+        <v>2.2633</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0833</v>
+        <v>0.103</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.8532</v>
+        <v>-3.235</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8273</v>
+        <v>-1.5356</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0259</v>
+        <v>-1.6994</v>
       </c>
       <c r="P7" t="n">
-        <v>1.0995</v>
+        <v>0.9163</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0995</v>
+        <v>1.8326</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5403</v>
+        <v>-0.28</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4955</v>
+        <v>0.5566</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0449</v>
+        <v>-0.8366</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6335</v>
+        <v>-0.3115</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X7" t="n">
         <v>-0.6335</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2701</v>
+        <v>-0.7225</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3609</v>
+        <v>-1.2096</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.4872</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9649</v>
@@ -1078,13 +1078,13 @@
         <v>1.4661</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8549</v>
+        <v>-0.3073</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0347</v>
+        <v>0.1859</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8895999999999999</v>
+        <v>-0.4932</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7713</v>
+        <v>-1.9852</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5171</v>
+        <v>1.2041</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.2884</v>
+        <v>-3.1893</v>
       </c>
       <c r="G9" t="n">
         <v>-3.6353</v>
@@ -1156,13 +1156,13 @@
         <v>1.0995</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1805</v>
+        <v>-0.3944</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6606</v>
+        <v>0.0264</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5199</v>
+        <v>-0.4208</v>
       </c>
       <c r="V9" t="n">
         <v>0.945</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. AZNAR MARTINEZ</t>
+          <t>K. MONTANO LINARES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8229</v>
+        <v>-2.7863</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7954</v>
+        <v>0.6851</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0275</v>
+        <v>-3.4715</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.138</v>
+        <v>-2.4593</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.66</v>
+        <v>0.5985</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.478</v>
+        <v>-3.0578</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.8664</v>
+        <v>2.0197</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3504</v>
+        <v>3.0896</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.516</v>
+        <v>-1.0699</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.2716</v>
+        <v>-4.479</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3097</v>
+        <v>-2.4911</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.962</v>
+        <v>-1.9879</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1833</v>
+        <v>0.9163</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.8326</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6493</v>
+        <v>2.7489</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4983</v>
+        <v>-0.2983</v>
       </c>
       <c r="T10" t="n">
-        <v>1.9035</v>
+        <v>0.4876</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4051</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.945</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.0104</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. MONTANO LINARES</t>
+          <t>J. BALLESTER FERRANDIS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5695</v>
+        <v>-3.5103</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.09810000000000001</v>
+        <v>-0.8002</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.4715</v>
+        <v>-2.7101</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.4593</v>
+        <v>-1.8857</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5985</v>
+        <v>-0.3214</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.0578</v>
+        <v>-1.5642</v>
       </c>
       <c r="J11" t="n">
-        <v>2.0197</v>
+        <v>0.305</v>
       </c>
       <c r="K11" t="n">
-        <v>3.0896</v>
+        <v>0.8111</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.0699</v>
+        <v>-0.5062</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.479</v>
+        <v>-2.1907</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.4911</v>
+        <v>-1.1326</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.9879</v>
+        <v>-1.0581</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9163</v>
+        <v>0.1833</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R11" t="n">
-        <v>2.7489</v>
+        <v>1.0995</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0814</v>
+        <v>-0.5409</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2956</v>
+        <v>-0.1889</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7858000000000001</v>
+        <v>-0.352</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.945</v>
+        <v>-1.267</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0104</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.9554</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. BALLESTER FERRANDIS</t>
+          <t>A. AZNAR MARTINEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.0272</v>
+        <v>-4.2572</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1437</v>
+        <v>-3.0315</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.8835</v>
+        <v>-1.2257</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.8857</v>
+        <v>-4.138</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3214</v>
+        <v>-2.66</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.5642</v>
+        <v>-1.478</v>
       </c>
       <c r="J12" t="n">
-        <v>0.305</v>
+        <v>-1.8664</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8111</v>
+        <v>-1.3504</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5062</v>
+        <v>-0.516</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.1907</v>
+        <v>-2.2716</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1326</v>
+        <v>-1.3097</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0581</v>
+        <v>-0.962</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1833</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R12" t="n">
-        <v>1.0995</v>
+        <v>1.6493</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0578</v>
+        <v>0.0641</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5324</v>
+        <v>0.6674</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5254</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.9917</v>
+        <v>-10.166</v>
       </c>
       <c r="E13" t="n">
-        <v>6.2548</v>
+        <v>7.0807</v>
       </c>
       <c r="F13" t="n">
         <v>-17.2466</v>
@@ -1435,7 +1435,7 @@
         <v>-13.0204</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.6856</v>
+        <v>-4.685600000000001</v>
       </c>
       <c r="I13" t="n">
         <v>-8.334899999999999</v>
@@ -1462,19 +1462,19 @@
         <v>6.414</v>
       </c>
       <c r="Q13" t="n">
-        <v>-8.246700000000001</v>
+        <v>-8.246699999999999</v>
       </c>
       <c r="R13" t="n">
         <v>14.6606</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.118300000000001</v>
+        <v>-2.2927</v>
       </c>
       <c r="T13" t="n">
-        <v>1.3577</v>
+        <v>2.1834</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.4758</v>
+        <v>-4.4759</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2669</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.8271</v>
+        <v>10.6124</v>
       </c>
       <c r="E14" t="n">
-        <v>10.8331</v>
+        <v>11.2177</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.006</v>
+        <v>-0.6052999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>9.4412</v>
@@ -1546,13 +1546,13 @@
         <v>1.0995</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4413</v>
+        <v>0.3441</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2549</v>
+        <v>0.6395</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6962</v>
+        <v>-0.2955</v>
       </c>
       <c r="V14" t="n">
         <v>0.6439</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. GARCIA ROYO</t>
+          <t>J. SABATE PRATS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0837</v>
+        <v>3.8042</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4044</v>
+        <v>2.9625</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6794</v>
+        <v>0.8418</v>
       </c>
       <c r="G15" t="n">
-        <v>2.9681</v>
+        <v>3.7085</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3305</v>
+        <v>1.6344</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3623</v>
+        <v>2.0742</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2203</v>
+        <v>4.6827</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1273</v>
+        <v>2.4801</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.907</v>
+        <v>2.2027</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2522</v>
+        <v>-0.9742</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.7968</v>
+        <v>-0.8457</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5446</v>
+        <v>-0.1285</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.4661</v>
+        <v>-2.3823</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.7489</v>
+        <v>-3.6651</v>
       </c>
       <c r="R15" t="n">
         <v>1.2828</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9482</v>
+        <v>0.8891</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2994</v>
+        <v>0.356</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6488</v>
+        <v>0.5332</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6335</v>
+        <v>1.5889</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6335</v>
+        <v>1.5889</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. SABATE PRATS</t>
+          <t>D. GARCIA ROYO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8392</v>
+        <v>3.3364</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1548</v>
+        <v>1.7313</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6844</v>
+        <v>1.6051</v>
       </c>
       <c r="G16" t="n">
-        <v>3.7085</v>
+        <v>2.9681</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6344</v>
+        <v>3.3305</v>
       </c>
       <c r="I16" t="n">
-        <v>2.0742</v>
+        <v>-0.3623</v>
       </c>
       <c r="J16" t="n">
-        <v>4.6827</v>
+        <v>3.2203</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4801</v>
+        <v>4.1273</v>
       </c>
       <c r="L16" t="n">
-        <v>2.2027</v>
+        <v>-0.907</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9742</v>
+        <v>-0.2522</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8457</v>
+        <v>-0.7968</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1285</v>
+        <v>0.5446</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.3823</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.6651</v>
+        <v>-2.7489</v>
       </c>
       <c r="R16" t="n">
         <v>1.2828</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9241</v>
+        <v>1.2008</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5483</v>
+        <v>0.6263</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3758</v>
+        <v>0.5744</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5889</v>
+        <v>0.6335</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5889</v>
+        <v>0.6335</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1979</v>
+        <v>1.3727</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5776</v>
+        <v>1.6738</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3797</v>
+        <v>-0.3011</v>
       </c>
       <c r="G18" t="n">
         <v>1.9005</v>
@@ -1858,13 +1858,13 @@
         <v>0.5498</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0142</v>
+        <v>0.1606</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0543</v>
+        <v>0.1505</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.0102</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3219</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. MORAGAS AZNAR</t>
+          <t>J. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0485</v>
+        <v>-0.1817</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2764</v>
+        <v>0.1513</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3249</v>
+        <v>-0.333</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.055</v>
+        <v>-1.5108</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5841</v>
+        <v>0.9187</v>
       </c>
       <c r="I20" t="n">
-        <v>0.529</v>
+        <v>-2.4295</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3865</v>
+        <v>0.3549</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5918</v>
+        <v>1.9507</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9782</v>
+        <v>-1.5958</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4415</v>
+        <v>-1.8658</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9923</v>
+        <v>-1.032</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4492</v>
+        <v>-0.8338</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.4661</v>
+        <v>0.1833</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2828</v>
+        <v>1.0995</v>
       </c>
       <c r="S20" t="n">
-        <v>2.2581</v>
+        <v>1.1459</v>
       </c>
       <c r="T20" t="n">
-        <v>2.086</v>
+        <v>0.7127</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1721</v>
+        <v>0.4332</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3115</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. CAMPOS DE BENGOA</t>
+          <t>J. VILLAR SOLER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4759</v>
+        <v>-0.5305</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2333</v>
+        <v>-1.2025</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2426</v>
+        <v>0.672</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5108</v>
+        <v>-1.0708</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9187</v>
+        <v>-0.1734</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.4295</v>
+        <v>-0.8974</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3549</v>
+        <v>-1.2387</v>
       </c>
       <c r="K21" t="n">
-        <v>1.9507</v>
+        <v>0.0433</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.5958</v>
+        <v>-1.2821</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.8658</v>
+        <v>0.1679</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.032</v>
+        <v>-0.2167</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8338</v>
+        <v>0.3846</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1833</v>
+        <v>0.3665</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0995</v>
+        <v>0.3665</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8517</v>
+        <v>0.1738</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3281</v>
+        <v>0.0362</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5236</v>
+        <v>0.1376</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. VILLAR SOLER</t>
+          <t>M. MORAGAS AZNAR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.58</v>
+        <v>-0.8257</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2025</v>
+        <v>-1.2379</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.4123</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0708</v>
+        <v>-1.055</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1734</v>
+        <v>-1.5841</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8974</v>
+        <v>0.529</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2387</v>
+        <v>0.3865</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0433</v>
+        <v>-0.5918</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2821</v>
+        <v>0.9782</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1679</v>
+        <v>-1.4415</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2167</v>
+        <v>-0.9923</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3846</v>
+        <v>-0.4492</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3665</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3665</v>
+        <v>1.2828</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1243</v>
+        <v>1.3839</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0362</v>
+        <v>1.1245</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0881</v>
+        <v>0.2594</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.3115</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1618</v>
+        <v>-1.1914</v>
       </c>
       <c r="E23" t="n">
-        <v>1.242</v>
+        <v>1.5305</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.4038</v>
+        <v>-2.7219</v>
       </c>
       <c r="G23" t="n">
         <v>0.2636</v>
@@ -2248,13 +2248,13 @@
         <v>0.5498</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1035</v>
+        <v>-0.1331</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1818</v>
+        <v>0.4702</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.2852</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9554</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.8144</v>
+        <v>-2.6906</v>
       </c>
       <c r="E24" t="n">
         <v>-2.1706</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6438</v>
+        <v>-0.52</v>
       </c>
       <c r="G24" t="n">
         <v>-1.3209</v>
@@ -2326,13 +2326,13 @@
         <v>0.3665</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0275</v>
+        <v>0.0963</v>
       </c>
       <c r="T24" t="n">
         <v>0.09130000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1188</v>
+        <v>0.0051</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.5736</v>
+        <v>-3.392</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.6834</v>
+        <v>-0.0103</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.8901</v>
+        <v>-3.3817</v>
       </c>
       <c r="G25" t="n">
         <v>-2.905</v>
@@ -2404,13 +2404,13 @@
         <v>0.3665</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.4016</v>
+        <v>-0.22</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4042</v>
+        <v>0.2689</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.9974</v>
+        <v>-0.4889</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6335</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>10.99160000000001</v>
+        <v>12.9147</v>
       </c>
       <c r="E26" t="n">
-        <v>17.2466</v>
+        <v>17.2467</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.254799999999999</v>
+        <v>-4.331799999999999</v>
       </c>
       <c r="G26" t="n">
         <v>13.0203</v>
@@ -2482,13 +2482,13 @@
         <v>8.246499999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>3.1183</v>
+        <v>5.0414</v>
       </c>
       <c r="T26" t="n">
-        <v>4.4761</v>
+        <v>4.476100000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.3577</v>
+        <v>0.5654000000000002</v>
       </c>
       <c r="V26" t="n">
         <v>1.267</v>
